--- a/templates/HEADWAY_ROLLING_STOCK_v1.0.xlsx
+++ b/templates/HEADWAY_ROLLING_STOCK_v1.0.xlsx
@@ -561,7 +561,7 @@
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>3. Row 3 contains an illustrative example row (marked with ID 'EXAMPLE_*'). Replace or delete before production use.</t>
+          <t>3. Row 3 contains a minimal valid baseline network for demonstration purposes. You may modify or replace it with your own railway data. The example is designed to load without validation errors.</t>
         </is>
       </c>
     </row>

--- a/templates/HEADWAY_ROLLING_STOCK_v1.0.xlsx
+++ b/templates/HEADWAY_ROLLING_STOCK_v1.0.xlsx
@@ -507,7 +507,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A16"/>
+  <dimension ref="A1:A17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="85" customWidth="1" min="1" max="1"/>
@@ -587,31 +587,38 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr"/>
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>7. For multi-link signalling blocks or TVS sections, define spatial geometry intervals in the 'BlockGeometry' or 'TVSGeometry' worksheet with sequential numbering.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="inlineStr">
+      <c r="A13" s="4" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
         <is>
           <t>WORKSHEET INVENTORY:</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t>• TrainTypes: Rolling stock types and kinematic parameters</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>• TractionCurves: Detailed tractive effort vs speed points (Optional)</t>
+          <t>• TrainTypes: Rolling stock types and kinematic parameters</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>• TractionCurves: Detailed tractive effort vs speed points (Optional)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
         <is>
           <t>• BrakingCurves: Detailed deceleration vs speed points (Optional)</t>
         </is>
